--- a/jogos_2025-01-23.xlsx
+++ b/jogos_2025-01-23.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>5.03</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>5.65</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.71</v>
+        <v>6.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['31', '56']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI4" t="n">
         <v>4.33</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45680.4375</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.5</v>
       </c>
-      <c r="O5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AD5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.38</v>
       </c>
-      <c r="X5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['31', '56']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45680.4375</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enyimba</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N7" t="n">
         <v>1.62</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.11</v>
-      </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AB7" t="n">
         <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['88', '9002']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '60']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.34</v>
+        <v>1.44</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45680.5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Enyimba</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="N8" t="n">
-        <v>1.62</v>
+        <v>5.11</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="R8" t="n">
         <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
         <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['88', '9002']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['4', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.9</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.44</v>
+        <v>3.34</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45680.5</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.67</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="AA18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['-1', '-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.88</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['27', '31']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45680.70833333334</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,65 +2862,65 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.36</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>['27', '31']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>1.17</v>
       </c>
       <c r="AI19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45680.70833333334</v>
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,43 +2991,43 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="M20" t="n">
         <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
         <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T20" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X20" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Y20" t="n">
         <v>2.88</v>
@@ -3036,38 +3036,38 @@
         <v>1.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.13</v>
+        <v>5.85</v>
       </c>
       <c r="AB20" t="n">
         <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['3', '9', '47']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['18', '26', '48']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45680.79166666666</v>
@@ -3094,69 +3094,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
         <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
         <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.62</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.61</v>
-      </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Y21" t="n">
         <v>2.88</v>
@@ -3165,38 +3165,38 @@
         <v>1.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.85</v>
+        <v>6.13</v>
       </c>
       <c r="AB21" t="n">
         <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['3', '9', '47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '26', '48']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45680.79166666666</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>2.63</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45680.89583333334</v>
@@ -3610,81 +3610,81 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X25" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA25" t="n">
-        <v>4</v>
+        <v>4.68</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AC25" t="n">
         <v>2.1</v>
@@ -3699,20 +3699,20 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['77', '86']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45680.89583333334</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,62 +3765,62 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="O26" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.67</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3828,20 +3828,20 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['77', '86']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45680.89583333334</v>
